--- a/projects.xlsx
+++ b/projects.xlsx
@@ -10,7 +10,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project Details" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Presales_POC" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="License" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Users" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sold_License" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Users" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R54"/>
+  <dimension ref="A1:T55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,60 +453,70 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>proj_type</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>start</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>due_date</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
         <is>
           <t>po</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>manual_hrs</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>auto_hrs</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>cost_per_hr</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>hours_saved</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>cost_saved</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>roi_pct</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>is_new</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>is_active</t>
         </is>
@@ -542,31 +553,35 @@
           <t>R&amp;M</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
         <is>
           <t>20/07/2025</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
         <is>
           <t>456788</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>GATE Entry and GRN Creation</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="b">
-        <v>1</v>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -597,38 +612,46 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Important</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
+          <t>RPA</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>22/09/2025</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>17/12/2025</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
         <is>
           <t>789747</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Downloading PO Creation Report</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="b">
-        <v>1</v>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -658,35 +681,39 @@
           <t>R&amp;M</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
         <is>
           <t>22/09/2025</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>19/01/2026</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
         <is>
           <t>984534</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Posting Cr amount to required Company code</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="b">
-        <v>1</v>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -718,29 +745,37 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
+          <t>RPA</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
           <t>22/09/2025</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>24/02/2026</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
         <is>
           <t>786540</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="b">
-        <v>0</v>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -770,31 +805,35 @@
           <t>UAT</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
         <is>
           <t>16/10/2025</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
         <is>
           <t>983240</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Creating Invoice Number by posting Material Number in SAP B1</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="b">
-        <v>1</v>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -824,26 +863,52 @@
           <t>PDD</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
         <is>
           <t>02/12/2026</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr">
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
         <is>
           <t>451238</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="b">
+      <c r="M7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 3</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> .30</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 10</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2.7</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>27.0</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="b">
         <v>1</v>
       </c>
     </row>
@@ -878,27 +943,31 @@
           <t>R&amp;M</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
         <is>
           <t>18/06/2022</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr">
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
         <is>
           <t>933248</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="b">
-        <v>1</v>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -928,27 +997,31 @@
           <t>R&amp;M</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
         <is>
           <t>20/04/2024</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
         <is>
           <t>84973</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="b">
-        <v>1</v>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -978,31 +1051,35 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
         <is>
           <t>20/11/2024</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>18/01/2025</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
         <is>
           <t>213480</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="b">
-        <v>1</v>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -1032,31 +1109,35 @@
           <t>R&amp;M</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
         <is>
           <t>01/03/2025</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>25/03/2025</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
         <is>
           <t>345576</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="b">
-        <v>1</v>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -1090,35 +1171,39 @@
           <t>R&amp;M</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
         <is>
           <t>04/03/2025</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>14/05/2025</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
         <is>
           <t>543778</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Moving data from SAP to Salesforce</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="b">
-        <v>1</v>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -1152,31 +1237,35 @@
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
         <is>
           <t>04/04/2025</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr">
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
         <is>
           <t>432670</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>Extraction of Specific data from PDFs</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="b">
-        <v>1</v>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -1206,35 +1295,39 @@
           <t>R&amp;M</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
         <is>
           <t>06/05/2025</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>28/02/2026</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
         <is>
           <t>355377</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>Identifying the correct batches in SAP B1</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="b">
-        <v>1</v>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -1264,31 +1357,35 @@
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
         <is>
           <t>06/10/2025</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr">
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
         <is>
           <t>872351</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>Organizing and prioritizing CTM tickets in Zendesk</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="b">
-        <v>1</v>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -1318,35 +1415,39 @@
           <t>R&amp;M</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
         <is>
           <t>09/03/2025</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>17/11/2025</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
         <is>
           <t>762345</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>Extracting the PO numbers from the PDFs</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="b">
-        <v>1</v>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -1376,31 +1477,35 @@
           <t>UAT</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
         <is>
           <t>30/09/2025</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr">
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
         <is>
           <t>672552</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>Creating quotations using data from SolidWorks BOM</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="b">
-        <v>1</v>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -1430,35 +1535,39 @@
           <t>R&amp;M</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
         <is>
           <t>01/08/2026</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>06/02/2026</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
         <is>
           <t>765428</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>Renaming and storing quality documents</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="b">
-        <v>1</v>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -1488,31 +1597,35 @@
           <t>UAT</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
         <is>
           <t>07/10/2025</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr">
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
         <is>
           <t>267357</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>Create TDS report and share to User</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="b">
-        <v>1</v>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -1542,31 +1655,35 @@
           <t>UAT</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
         <is>
           <t>07/10/2025</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr">
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
         <is>
           <t>872610</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>Create GST report and share to User</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="b">
-        <v>1</v>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -1596,35 +1713,39 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
         <is>
           <t>22/08/2025</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
         <is>
           <t>465738</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>Check for cancellation jobs in SAP and send alert mail</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="b">
-        <v>1</v>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -1654,35 +1775,39 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
         <is>
           <t>24/10/2025</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
         <is>
           <t>749474</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>Check for Active jobs in SAP and send alert mail</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="b">
-        <v>1</v>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -1712,31 +1837,35 @@
           <t>UAT</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
         <is>
           <t>14/11/2025</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr">
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
         <is>
           <t>248490</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>Download the fixture dump data and append every 2 mins</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="b">
-        <v>1</v>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -1768,25 +1897,29 @@
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr">
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
         <is>
           <t>353628</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>Need to post the invoices</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="b">
-        <v>1</v>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
     </row>
     <row r="25">
@@ -1816,35 +1949,39 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
         <is>
           <t>06/08/2025</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>06/11/2025</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
         <is>
           <t>235367</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>Need to confirm the vendor codes</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="b">
-        <v>1</v>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
     </row>
     <row r="26">
@@ -1874,35 +2011,39 @@
           <t>R&amp;M</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
         <is>
           <t>01/07/2025</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>21/01/2026</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
         <is>
           <t>484640</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>Downloading Block Stock Report and send to user</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="b">
-        <v>1</v>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
     </row>
     <row r="27">
@@ -1932,31 +2073,35 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
         <is>
           <t>12/02/2025</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr">
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
         <is>
           <t>674537</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>Reserve the tool crib data in FIFO Order</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="b">
-        <v>1</v>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
     </row>
     <row r="28">
@@ -1986,31 +2131,35 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
         <is>
           <t>12/02/2025</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr">
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
         <is>
           <t>380273</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>Post Goods Issue to movement type 201</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="b">
-        <v>1</v>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
     </row>
     <row r="29">
@@ -2040,31 +2189,35 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
         <is>
           <t>02/10/2026</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr">
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
         <is>
           <t>345468</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>Download the QA32 Dump file and append every 2 mins</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="b">
-        <v>1</v>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
     </row>
     <row r="30">
@@ -2094,31 +2247,35 @@
           <t>PDD</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
         <is>
           <t>13/02/2026</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr">
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
         <is>
           <t>189375</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>Create Finance Report</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="b">
-        <v>1</v>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
     </row>
     <row r="31">
@@ -2148,35 +2305,39 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
         <is>
           <t>26/12/2026</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>05/02/2026</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
         <is>
           <t>345465</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>Downloading and Updating Employee Assembly and Raw Clock data</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="b">
-        <v>1</v>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -2217,8 +2378,12 @@
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="b">
-        <v>1</v>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
     </row>
     <row r="33">
@@ -2259,8 +2424,12 @@
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="b">
-        <v>1</v>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
     </row>
     <row r="34">
@@ -2287,34 +2456,38 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Internal POC</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
         <is>
           <t>15/12/2025</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>10/01/2026</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr">
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
         <is>
           <t>Agentic Platform using Google Cloud and NotebookLM</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="b">
-        <v>1</v>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
     </row>
     <row r="35">
@@ -2341,34 +2514,38 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Internal POC</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
         <is>
           <t>05/11/2025</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>14/11/2025</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr">
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
         <is>
           <t>Agentic Platform using Microsoft Copilot Frontier</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="b">
-        <v>1</v>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
     </row>
     <row r="36">
@@ -2387,38 +2564,50 @@
           <t>Internal POC</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Sushma</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Faiyaz</t>
+          <t>Faiyaz, Nanditha, Radhika, Sharan, Soumya</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Internal POC</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
+          <t>RPA</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
           <t>07/01/2026</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr">
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
         <is>
           <t>Explored TestManager, Test Cloud and Test Automation</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="b">
-        <v>1</v>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
     </row>
     <row r="37">
@@ -2445,34 +2634,38 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Internal POC</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
         <is>
           <t>10/03/2025</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>14/05/2025</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr">
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
         <is>
           <t>Chat with PDF AI</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="b">
-        <v>1</v>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
     </row>
     <row r="38">
@@ -2494,39 +2687,43 @@
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Chandru S &amp; Sivin</t>
+          <t>Chandru S, Sivin</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Internal POC</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
         <is>
           <t>22/05/2025</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>20/06/2025</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr">
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
         <is>
           <t>Conversion of Medicare Insurance PDF to EDI</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="b">
-        <v>1</v>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
     </row>
     <row r="39">
@@ -2553,30 +2750,34 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Internal POC</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
         <is>
           <t>02/06/2025</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr">
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
         <is>
           <t>Agentic Platform using Krista.ai</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="b">
-        <v>1</v>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
     </row>
     <row r="40">
@@ -2603,34 +2804,38 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Internal POC</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
         <is>
           <t>20/06/2025</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>24/06/2025</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr">
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
         <is>
           <t>Integrated UiPath usecases with GitHub</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="b">
-        <v>1</v>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
     </row>
     <row r="41">
@@ -2657,30 +2862,34 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Internal POC</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
         <is>
           <t>10/11/2025</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr">
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
         <is>
           <t>Agentic Platform using Microsoft Copilot Studio</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr"/>
-      <c r="R41" t="b">
-        <v>1</v>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
     </row>
     <row r="42">
@@ -2707,34 +2916,38 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Internal POC</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
         <is>
           <t>07/07/2025</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>09/07/2025</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr">
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
         <is>
           <t>Agentic Platform using N8N</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr"/>
-      <c r="R42" t="b">
-        <v>1</v>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
     </row>
     <row r="43">
@@ -2761,30 +2974,34 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Internal POC</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
         <is>
           <t>04/02/2026</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr">
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
         <is>
           <t>Explored UiPath On-premise Studio, Orchestrator, Test Suite</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr"/>
-      <c r="R43" t="b">
-        <v>1</v>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="inlineStr"/>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
     </row>
     <row r="44">
@@ -2811,34 +3028,38 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Internal POC</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
         <is>
           <t>24/01/2026</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>23/01/2026</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr">
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
         <is>
           <t>Web Development Project Tracker</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr"/>
-      <c r="R44" t="b">
-        <v>1</v>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
     </row>
     <row r="45">
@@ -2865,34 +3086,38 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Internal POC</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
         <is>
           <t>02/02/2026</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>05/02/2026</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr">
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
         <is>
           <t>Agentic Platform using Amazon Bedrock and S3 bucket</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr"/>
-      <c r="R45" t="b">
-        <v>1</v>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="inlineStr"/>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
     </row>
     <row r="46">
@@ -2919,34 +3144,38 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>External POC</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
         <is>
           <t>17/02/2026</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr">
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
         <is>
           <t>Reconciliation of Files to create a template</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="b">
-        <v>1</v>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
     </row>
     <row r="47">
@@ -2973,7 +3202,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Internal POC</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
@@ -2987,8 +3216,12 @@
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr"/>
-      <c r="R47" t="b">
-        <v>1</v>
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="inlineStr"/>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
     </row>
     <row r="48">
@@ -3018,27 +3251,31 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr">
         <is>
           <t>2026-03-16 00:00:00</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr">
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
         <is>
           <t>Posting Pick list data</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr"/>
-      <c r="R48" t="b">
-        <v>1</v>
+      <c r="R48" t="inlineStr"/>
+      <c r="S48" t="inlineStr"/>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
     </row>
     <row r="49">
@@ -3074,25 +3311,33 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
+          <t>AI Agent</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr">
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
         <is>
           <t>AI Boot Camp</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr"/>
-      <c r="R49" t="b">
-        <v>1</v>
+      <c r="R49" t="inlineStr"/>
+      <c r="S49" t="inlineStr"/>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
     </row>
     <row r="50">
@@ -3122,12 +3367,12 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr">
         <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
@@ -3137,8 +3382,12 @@
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr"/>
-      <c r="R50" t="b">
-        <v>1</v>
+      <c r="R50" t="inlineStr"/>
+      <c r="S50" t="inlineStr"/>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
     </row>
     <row r="51">
@@ -3168,27 +3417,31 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr">
         <is>
           <t>12/03/2026</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr">
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
         <is>
           <t>Submitting matching records in SAP B1 after doing reconciliation</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr"/>
-      <c r="R51" t="b">
-        <v>1</v>
+      <c r="R51" t="inlineStr"/>
+      <c r="S51" t="inlineStr"/>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
     </row>
     <row r="52">
@@ -3224,25 +3477,33 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
+          <t>AI Agent</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr">
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
         <is>
           <t>Working on Claude</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr"/>
       <c r="Q52" t="inlineStr"/>
-      <c r="R52" t="b">
-        <v>1</v>
+      <c r="R52" t="inlineStr"/>
+      <c r="S52" t="inlineStr"/>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
     </row>
     <row r="53">
@@ -3276,31 +3537,35 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr">
         <is>
           <t>01/10/2025</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr">
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
         <is>
           <t>Full time Contract employee for Infosys</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr"/>
       <c r="Q53" t="inlineStr"/>
-      <c r="R53" t="b">
-        <v>1</v>
+      <c r="R53" t="inlineStr"/>
+      <c r="S53" t="inlineStr"/>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
     </row>
     <row r="54">
@@ -3330,12 +3595,12 @@
           <t>Presales</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr">
         <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
@@ -3343,14 +3608,84 @@
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
+      <c r="P54" t="inlineStr"/>
       <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="b">
-        <v>1</v>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr"/>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Raychem - Outward</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Raychem</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Vishnu</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Radhika</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Presales</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>working on Getting project</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr"/>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -3364,7 +3699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R16"/>
+  <dimension ref="A1:T2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3400,60 +3735,70 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>proj_type</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>start</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>due_date</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
         <is>
           <t>po</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>manual_hrs</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>auto_hrs</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>cost_per_hr</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>hours_saved</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>cost_saved</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>roi_pct</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>is_new</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>is_active</t>
         </is>
@@ -3462,46 +3807,38 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>54</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Google Cloud Platform</t>
+          <t>Raychem</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Internal POC</t>
+          <t>Raychem</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Faiyaz</t>
+          <t>Vishnu</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Internal POC</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>15/12/2025</t>
-        </is>
-      </c>
+          <t>Presales</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>10/01/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Agentic Platform using Google Cloud and NotebookLM</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
@@ -3509,732 +3846,16 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Microsoft Agent Frontier</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Internal POC</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Faiyaz</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Internal POC</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>05/11/2025</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>14/11/2025</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Agentic Platform using Microsoft Copilot Frontier</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>UiPath Test Automation</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Internal POC</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Faiyaz</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Internal POC</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>07/01/2026</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Explored TestManager, Test Cloud and Test Automation</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Qpdf</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Internal POC</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Chandru S</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Internal POC</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>10/03/2025</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>14/05/2025</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Chat with PDF AI</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>EDI</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Internal POC</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Chandru S &amp; Sivin</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Internal POC</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>22/05/2025</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>20/06/2025</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Conversion of Medicare Insurance PDF to EDI</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>krista.ai</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Internal POC</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Chandru S</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Internal POC</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>02/06/2025</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Agentic Platform using Krista.ai</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>UiPath with GitHub</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Internal POC</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Chandru S</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Internal POC</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>20/06/2025</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>24/06/2025</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Integrated UiPath usecases with GitHub</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Microsoft Copilot Agent with Studio</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Internal POC</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Chandru S</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Internal POC</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>10/11/2025</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Agentic Platform using Microsoft Copilot Studio</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>N8N</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Internal POC</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Chandru S</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Internal POC</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>07/07/2025</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>09/07/2025</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Agentic Platform using N8N</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>UiPath Standalone</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Internal POC</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Chandru S</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Internal POC</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>04/02/2026</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Explored UiPath On-premise Studio, Orchestrator, Test Suite</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>SHAREPOINT</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Internal POC</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Rubika AE</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Internal POC</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>24/01/2026</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>23/01/2026</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Web Development Project Tracker</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>AWS - Knowledge Based Agent</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Internal POC</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Rubika AE</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Internal POC</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>02/02/2026</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>05/02/2026</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Agentic Platform using Amazon Bedrock and S3 bucket</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Himatsingha</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>External POC</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Narendra</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>External POC</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>17/02/2026</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>14/03/2026</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Reconciliation of Files to create a template</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>IBM RPA Tool</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Internal POC</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Sharan</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Internal POC</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Raychem</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Raychem</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Vishnu</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Presales</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="b">
-        <v>1</v>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -4317,11 +3938,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Uipath</t>
+          <t>Uipath - ROBOT</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -4350,6 +3971,214 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>tool_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>client</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>no_of_licenses</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>start_date</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>end_date</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Uipath - ROBOT</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>TEPL</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>MSB Model</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2026-05-05T13:41:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Uipath - ROBOT</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Swagelok - Alabama</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>MSB Model</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2026-05-05T13:40:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Uipath - ROBOT</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Swagelok - California</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>MSB Model</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2026-05-05T13:40:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Uipath - ROBOT</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Raychem</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>MSB Model</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2026-05-05T13:39:12</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>

--- a/projects.xlsx
+++ b/projects.xlsx
@@ -908,8 +908,10 @@
         </is>
       </c>
       <c r="S7" t="inlineStr"/>
-      <c r="T7" t="b">
-        <v>1</v>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -4179,7 +4181,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4382,6 +4384,510 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Sushma Rajolli</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>sushma.g@qualesce.com</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>lead</t>
+        </is>
+      </c>
+      <c r="E8" t="b">
+        <v>1</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-05-06T12:04:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Avinash Kumar</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>avinash.k@qualesce.com</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>employee</t>
+        </is>
+      </c>
+      <c r="E9" t="b">
+        <v>1</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-05-06T12:04:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Nandita Radhakrishna</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>nandita.r@qualesce.com</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>lead</t>
+        </is>
+      </c>
+      <c r="E10" t="b">
+        <v>1</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-05-06T12:04:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Soumya Balayya kalal</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>soumya.s@qualesce.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>lead</t>
+        </is>
+      </c>
+      <c r="E11" t="b">
+        <v>1</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-05-06T12:04:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Chethan B N</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>chethan.b@qualesce.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>lead</t>
+        </is>
+      </c>
+      <c r="E12" t="b">
+        <v>1</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-05-06T12:04:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>MathanPrasath</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>mathan.p@qualesce.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>employee</t>
+        </is>
+      </c>
+      <c r="E13" t="b">
+        <v>1</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-05-06T12:04:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Yashwanth H P</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>yashwanth.hp@qualesce.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>employee</t>
+        </is>
+      </c>
+      <c r="E14" t="b">
+        <v>1</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-05-06T12:04:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Radhika</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>rubika.ae@qualesce.com</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>employee</t>
+        </is>
+      </c>
+      <c r="E15" t="b">
+        <v>1</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-05-06T12:04:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Akhila Kovuri</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>akhila.k@qualesce.com</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>employee</t>
+        </is>
+      </c>
+      <c r="E16" t="b">
+        <v>1</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-05-06T12:04:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Sharanbasappa Malipatil</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>sharanbasappa.m@qualesce.com</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>employee</t>
+        </is>
+      </c>
+      <c r="E17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-05-06T12:04:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Nandukant Bhaskar</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>nandukant.b@qualesce.com</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>employee</t>
+        </is>
+      </c>
+      <c r="E18" t="b">
+        <v>1</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-05-06T12:04:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Narendra C</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>narendra.c@qualesce.com</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>employee</t>
+        </is>
+      </c>
+      <c r="E19" t="b">
+        <v>1</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-05-06T12:04:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Vikas Baburao Sajjan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>vikasbaburao.sajjan@qualesce.com</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>employee</t>
+        </is>
+      </c>
+      <c r="E20" t="b">
+        <v>1</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-05-06T12:04:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Shravani S</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>shravani.s@qualesce.com</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>employee</t>
+        </is>
+      </c>
+      <c r="E21" t="b">
+        <v>1</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-05-06T12:04:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Shiva shankar</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>shiva.shankarb@qualesce.com</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>employee</t>
+        </is>
+      </c>
+      <c r="E22" t="b">
+        <v>1</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-05-06T12:04:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Nischal</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>nischal.n@qualesce.com</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>employee</t>
+        </is>
+      </c>
+      <c r="E23" t="b">
+        <v>1</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-05-06T12:04:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Harshith</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>harshith.v@qualesce.com</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>employee</t>
+        </is>
+      </c>
+      <c r="E24" t="b">
+        <v>1</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-05-06T12:04:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Nanditha</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>nandhitha.g@qualesce.com</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>employee</t>
+        </is>
+      </c>
+      <c r="E25" t="b">
+        <v>1</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-05-06T12:04:11</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/projects.xlsx
+++ b/projects.xlsx
@@ -4181,7 +4181,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4582,16 +4582,16 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Radhika</t>
+          <t>Akhila Kovuri</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>rubika.ae@qualesce.com</t>
+          <t>akhila.k@qualesce.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -4604,22 +4604,22 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-05-06T12:04:08</t>
+          <t>2026-05-06T12:04:09</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Akhila Kovuri</t>
+          <t>Sharanbasappa Malipatil</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>akhila.k@qualesce.com</t>
+          <t>sharanbasappa.m@qualesce.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -4638,16 +4638,16 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sharanbasappa Malipatil</t>
+          <t>Nandukant Bhaskar</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>sharanbasappa.m@qualesce.com</t>
+          <t>nandukant.b@qualesce.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -4666,16 +4666,16 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Nandukant Bhaskar</t>
+          <t>Narendra C</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>nandukant.b@qualesce.com</t>
+          <t>narendra.c@qualesce.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -4694,16 +4694,16 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Narendra C</t>
+          <t>Vikas Baburao Sajjan</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>narendra.c@qualesce.com</t>
+          <t>vikasbaburao.sajjan@qualesce.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4716,22 +4716,22 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-05-06T12:04:09</t>
+          <t>2026-05-06T12:04:10</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Vikas Baburao Sajjan</t>
+          <t>Shravani S</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>vikasbaburao.sajjan@qualesce.com</t>
+          <t>shravani.s@qualesce.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4750,16 +4750,16 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Shravani S</t>
+          <t>Shiva shankar</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>shravani.s@qualesce.com</t>
+          <t>shiva.shankarb@qualesce.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4778,16 +4778,16 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Shiva shankar</t>
+          <t>Nischal</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>shiva.shankarb@qualesce.com</t>
+          <t>nischal.n@qualesce.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4806,16 +4806,16 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Nischal</t>
+          <t>Harshith</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>nischal.n@qualesce.com</t>
+          <t>harshith.v@qualesce.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4834,16 +4834,16 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Harshith</t>
+          <t>Nanditha</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>harshith.v@qualesce.com</t>
+          <t>nandhitha.g@qualesce.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4855,34 +4855,6 @@
         <v>1</v>
       </c>
       <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-05-06T12:04:10</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Nanditha</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>nandhitha.g@qualesce.com</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>employee</t>
-        </is>
-      </c>
-      <c r="E25" t="b">
-        <v>1</v>
-      </c>
-      <c r="F25" t="inlineStr">
         <is>
           <t>2026-05-06T12:04:11</t>
         </is>

--- a/projects.xlsx
+++ b/projects.xlsx
@@ -12,6 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="License" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sold_License" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Users" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tasks" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4863,4 +4864,682 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>progress</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>due_date</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>start_date</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>assigned_to</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>assigned_to_email</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>assigned_by</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>assigned_by_email</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>DASHBOARD TESTING</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2026-05-06T16:16:56</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2026-05-06T16:16:56</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Chandru</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>chandru.s@qualesce.com</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>admin@qualesce.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>TESTING</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2026-05-06T16:16:28</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2026-05-06T16:16:28</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Chandru</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>chandru.s@qualesce.com</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>admin@qualesce.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>TESTING</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2026-05-06T16:16:19</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2026-05-06T16:16:19</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Chandru</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>chandru.s@qualesce.com</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>admin@qualesce.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Notification Test</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2026-05-06T13:52:29</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2026-05-06T13:52:29</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Chandru</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>chandru.s@qualesce.com</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Vikram</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>vikram.r@qualesce.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Agentic AI(Claude)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>15</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2026-05-06T13:22:54</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2026-05-06T13:29:49</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Chandru</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>chandru.s@qualesce.com</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>admin@qualesce.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>TestAutomation</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>30</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2026-05-04T17:33:01</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2026-05-06T11:49:30</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Vikram</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>vikram.r@qualesce.com</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>admin@qualesce.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Dashboard Creation</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2026-04-29T13:03:34</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-04-29T13:03:34</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Vikram</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>vikram.r@qualesce.com</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>admin@qualesce.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Claude Automation</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2026-04-28T16:44:42</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2026-04-28T16:44:42</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Chandru</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>chandru.s@qualesce.com</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>admin@qualesce.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>2</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Test Automation</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>UIpath Test Automation</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>25</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2026-04-28T11:30:37</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2026-04-28T11:42:37</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Chandru</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>chandru.s@qualesce.com</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Vikram</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>vikram.r@qualesce.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ai</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Testing Ai tools</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>10</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2026-04-28T11:27:13</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2026-04-28T11:27:50</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Chandru</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>chandru.s@qualesce.com</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>admin@qualesce.com</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>